--- a/data/词句数据.xlsx
+++ b/data/词句数据.xlsx
@@ -2488,7 +2488,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I461"/>
+  <dimension ref="A1:I509"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -15859,9 +15859,1401 @@
         <v/>
       </c>
     </row>
+    <row r="462">
+      <c r="A462" t="str">
+        <v>宠辱不惊，看庭前花开花落；去留无意，望天上云卷云舒。</v>
+      </c>
+      <c r="B462" t="str">
+        <v>《菜根谭》</v>
+      </c>
+      <c r="C462" t="str">
+        <v>菜根谭</v>
+      </c>
+      <c r="D462" t="str">
+        <v>明</v>
+      </c>
+      <c r="E462" t="str">
+        <v>zhichang</v>
+      </c>
+      <c r="F462" t="str">
+        <v>chaoran,pingjing</v>
+      </c>
+      <c r="G462" t="str">
+        <v>被表扬或被排挤都别太当回事，用这句稳住心态。</v>
+      </c>
+      <c r="H462" t="str">
+        <v/>
+      </c>
+      <c r="I462" t="str">
+        <v>荣耀羞辱都不动心，去留都不挂怀，只看好花开花落、云卷云舒。</v>
+      </c>
+    </row>
+    <row r="463">
+      <c r="A463" t="str">
+        <v>采得百花成蜜后，为谁辛苦为谁甜？</v>
+      </c>
+      <c r="B463" t="str">
+        <v>罗隐</v>
+      </c>
+      <c r="C463" t="str">
+        <v>蜂</v>
+      </c>
+      <c r="D463" t="str">
+        <v>唐</v>
+      </c>
+      <c r="E463" t="str">
+        <v>zhichang</v>
+      </c>
+      <c r="F463" t="str">
+        <v>chensi,buping</v>
+      </c>
+      <c r="G463" t="str">
+        <v>熬夜替别人做嫁衣时，半开玩笑发一句。</v>
+      </c>
+      <c r="H463" t="str">
+        <v/>
+      </c>
+      <c r="I463" t="str">
+        <v>采尽百花酿成蜜，到底为谁辛苦为谁甜？</v>
+      </c>
+    </row>
+    <row r="464">
+      <c r="A464" t="str">
+        <v>沧浪之水清兮，可以濯吾缨；沧浪之水浊兮，可以濯吾足。</v>
+      </c>
+      <c r="B464" t="str">
+        <v>屈原</v>
+      </c>
+      <c r="C464" t="str">
+        <v>渔父</v>
+      </c>
+      <c r="D464" t="str">
+        <v>战国</v>
+      </c>
+      <c r="E464" t="str">
+        <v>zhichang</v>
+      </c>
+      <c r="F464" t="str">
+        <v>chaoran,canglang</v>
+      </c>
+      <c r="G464" t="str">
+        <v>环境好坏都得活下去，用这句表达随遇而安。</v>
+      </c>
+      <c r="H464" t="str">
+        <v/>
+      </c>
+      <c r="I464" t="str">
+        <v>水清就洗帽带，水浊就洗脚——处境不同，应对不同。</v>
+      </c>
+    </row>
+    <row r="465">
+      <c r="A465" t="str">
+        <v>桐花万里丹山路，雏凤清于老凤声。</v>
+      </c>
+      <c r="B465" t="str">
+        <v>李商隐</v>
+      </c>
+      <c r="C465" t="str">
+        <v>韩冬郎即席为诗相送</v>
+      </c>
+      <c r="D465" t="str">
+        <v>唐</v>
+      </c>
+      <c r="E465" t="str">
+        <v>shengzhi</v>
+      </c>
+      <c r="F465" t="str">
+        <v>zhuangzhi,kuangxi</v>
+      </c>
+      <c r="G465" t="str">
+        <v>年轻人被认可、后辈超车，用这句夸自己也夸势头。</v>
+      </c>
+      <c r="H465" t="str">
+        <v/>
+      </c>
+      <c r="I465" t="str">
+        <v>万里丹山桐花盛开，雏凤的鸣声比老凤更清亮。</v>
+      </c>
+    </row>
+    <row r="466">
+      <c r="A466" t="str">
+        <v>仰天大笑出门去，我辈岂是蓬蒿人。</v>
+      </c>
+      <c r="B466" t="str">
+        <v>李白</v>
+      </c>
+      <c r="C466" t="str">
+        <v>南陵别儿童入京</v>
+      </c>
+      <c r="D466" t="str">
+        <v>唐</v>
+      </c>
+      <c r="E466" t="str">
+        <v>luobang</v>
+      </c>
+      <c r="F466" t="str">
+        <v>haomai,kuangxi</v>
+      </c>
+      <c r="G466" t="str">
+        <v>落榜但底气还在，发这句嘲讽一下看轻你的人。</v>
+      </c>
+      <c r="H466" t="str">
+        <v/>
+      </c>
+      <c r="I466" t="str">
+        <v>仰天大笑走出门去，我哪是久居草野的平凡人。</v>
+      </c>
+    </row>
+    <row r="467">
+      <c r="A467" t="str">
+        <v>古来青史谁不见，今见功名胜古人。</v>
+      </c>
+      <c r="B467" t="str">
+        <v>李白</v>
+      </c>
+      <c r="C467" t="str">
+        <v>赠郭将军</v>
+      </c>
+      <c r="D467" t="str">
+        <v>唐</v>
+      </c>
+      <c r="E467" t="str">
+        <v>luobang</v>
+      </c>
+      <c r="F467" t="str">
+        <v>zhuangzhi,haomai</v>
+      </c>
+      <c r="G467" t="str">
+        <v>这次没成，但相信下次功劳胜过前人，发来立誓。</v>
+      </c>
+      <c r="H467" t="str">
+        <v/>
+      </c>
+      <c r="I467" t="str">
+        <v>自古青史留名谁人不见，如今要建立胜过古人的功业。</v>
+      </c>
+    </row>
+    <row r="468">
+      <c r="A468" t="str">
+        <v>桃李春风一杯酒，江湖夜雨十年灯。</v>
+      </c>
+      <c r="B468" t="str">
+        <v>黄庭坚</v>
+      </c>
+      <c r="C468" t="str">
+        <v>寄黄几复</v>
+      </c>
+      <c r="D468" t="str">
+        <v>宋</v>
+      </c>
+      <c r="E468" t="str">
+        <v>tongchuang</v>
+      </c>
+      <c r="F468" t="str">
+        <v>sinian,zhenxi</v>
+      </c>
+      <c r="G468" t="str">
+        <v>和老同学老战友叙旧，发这句讲那份隔了年的交情。</v>
+      </c>
+      <c r="H468" t="str">
+        <v/>
+      </c>
+      <c r="I468" t="str">
+        <v>当年春风里共饮一杯酒，如今江湖夜雨对着十年孤灯——都在想你。</v>
+      </c>
+    </row>
+    <row r="469">
+      <c r="A469" t="str">
+        <v>同是天涯沦落人，相逢何必曾相识。</v>
+      </c>
+      <c r="B469" t="str">
+        <v>白居易</v>
+      </c>
+      <c r="C469" t="str">
+        <v>琵琶行</v>
+      </c>
+      <c r="D469" t="str">
+        <v>唐</v>
+      </c>
+      <c r="E469" t="str">
+        <v>tongchuang</v>
+      </c>
+      <c r="F469" t="str">
+        <v>zhenxi,gudu</v>
+      </c>
+      <c r="G469" t="str">
+        <v>和一起扛过事的兄弟感慨际遇，发这句最对味。</v>
+      </c>
+      <c r="H469" t="str">
+        <v/>
+      </c>
+      <c r="I469" t="str">
+        <v>同样漂泊沦落，相逢何必曾是旧识。</v>
+      </c>
+    </row>
+    <row r="470">
+      <c r="A470" t="str">
+        <v>少年乐相知，衰暮思故友。</v>
+      </c>
+      <c r="B470" t="str">
+        <v>韩愈</v>
+      </c>
+      <c r="C470" t="str">
+        <v>除官赴阙至江州寄鄂岳李大夫</v>
+      </c>
+      <c r="D470" t="str">
+        <v>唐</v>
+      </c>
+      <c r="E470" t="str">
+        <v>tongchuang</v>
+      </c>
+      <c r="F470" t="str">
+        <v>zhenxi,sinian</v>
+      </c>
+      <c r="G470" t="str">
+        <v>年纪渐长想起当年同窗，用这句发条感慨。</v>
+      </c>
+      <c r="H470" t="str">
+        <v/>
+      </c>
+      <c r="I470" t="str">
+        <v>年少时以相交为乐，年老了思念老友。</v>
+      </c>
+    </row>
+    <row r="471">
+      <c r="A471" t="str">
+        <v>人面不知何处去，桃花依旧笑春风。</v>
+      </c>
+      <c r="B471" t="str">
+        <v>崔护</v>
+      </c>
+      <c r="C471" t="str">
+        <v>题都城南庄</v>
+      </c>
+      <c r="D471" t="str">
+        <v>唐</v>
+      </c>
+      <c r="E471" t="str">
+        <v>jiuzhao</v>
+      </c>
+      <c r="F471" t="str">
+        <v>sinian,chensi</v>
+      </c>
+      <c r="G471" t="str">
+        <v>旧物还在、人已不在，用这句替那份物是人非叹口气。</v>
+      </c>
+      <c r="H471" t="str">
+        <v/>
+      </c>
+      <c r="I471" t="str">
+        <v>当年的人不知去了哪，桃花却仍笑着迎春风。</v>
+      </c>
+    </row>
+    <row r="472">
+      <c r="A472" t="str">
+        <v>当时共我赏花人，点检如今无一半。</v>
+      </c>
+      <c r="B472" t="str">
+        <v>晏殊</v>
+      </c>
+      <c r="C472" t="str">
+        <v>木兰花</v>
+      </c>
+      <c r="D472" t="str">
+        <v>宋</v>
+      </c>
+      <c r="E472" t="str">
+        <v>jiuzhao</v>
+      </c>
+      <c r="F472" t="str">
+        <v>sinian,gudu</v>
+      </c>
+      <c r="G472" t="str">
+        <v>老照片里的人走了一半，发这句数一数还在的。</v>
+      </c>
+      <c r="H472" t="str">
+        <v/>
+      </c>
+      <c r="I472" t="str">
+        <v>当年陪我赏花的人，数一数如今剩不到一半。</v>
+      </c>
+    </row>
+    <row r="473">
+      <c r="A473" t="str">
+        <v>十年磨一剑，霜刃未曾试。</v>
+      </c>
+      <c r="B473" t="str">
+        <v>贾岛</v>
+      </c>
+      <c r="C473" t="str">
+        <v>剑客</v>
+      </c>
+      <c r="D473" t="str">
+        <v>唐</v>
+      </c>
+      <c r="E473" t="str">
+        <v>duokui</v>
+      </c>
+      <c r="F473" t="str">
+        <v>zhuangzhi,jueqiang</v>
+      </c>
+      <c r="G473" t="str">
+        <v>憋了很久终于拿结果，用这句说剑该出鞘了。</v>
+      </c>
+      <c r="H473" t="str">
+        <v/>
+      </c>
+      <c r="I473" t="str">
+        <v>磨了十年的一把剑，寒光凛凛还没试过。</v>
+      </c>
+    </row>
+    <row r="474">
+      <c r="A474" t="str">
+        <v>但使龙城飞将在，不教胡马度阴山。</v>
+      </c>
+      <c r="B474" t="str">
+        <v>王昌龄</v>
+      </c>
+      <c r="C474" t="str">
+        <v>出塞</v>
+      </c>
+      <c r="D474" t="str">
+        <v>唐</v>
+      </c>
+      <c r="E474" t="str">
+        <v>duokui</v>
+      </c>
+      <c r="F474" t="str">
+        <v>zhuangzhi,haomai</v>
+      </c>
+      <c r="G474" t="str">
+        <v>团队夺冠、守住阵地，用这句夸你们这拨人。</v>
+      </c>
+      <c r="H474" t="str">
+        <v/>
+      </c>
+      <c r="I474" t="str">
+        <v>只要有飞将军在，绝不让敌人跨过阴山。</v>
+      </c>
+    </row>
+    <row r="475">
+      <c r="A475" t="str">
+        <v>欲说还休，欲说还休，却道天凉好个秋。</v>
+      </c>
+      <c r="B475" t="str">
+        <v>辛弃疾</v>
+      </c>
+      <c r="C475" t="str">
+        <v>丑奴儿</v>
+      </c>
+      <c r="D475" t="str">
+        <v>宋</v>
+      </c>
+      <c r="E475" t="str">
+        <v>wuji</v>
+      </c>
+      <c r="F475" t="str">
+        <v>sinian,gudu</v>
+      </c>
+      <c r="G475" t="str">
+        <v>话到嘴边又咽下，发这句比直说更让人懂。</v>
+      </c>
+      <c r="H475" t="str">
+        <v/>
+      </c>
+      <c r="I475" t="str">
+        <v>想说又停住，最后只说一句天凉好个秋。</v>
+      </c>
+    </row>
+    <row r="476">
+      <c r="A476" t="str">
+        <v>相思相见知何日？此时此夜难为情。</v>
+      </c>
+      <c r="B476" t="str">
+        <v>李白</v>
+      </c>
+      <c r="C476" t="str">
+        <v>秋风词</v>
+      </c>
+      <c r="D476" t="str">
+        <v>唐</v>
+      </c>
+      <c r="E476" t="str">
+        <v>wuji</v>
+      </c>
+      <c r="F476" t="str">
+        <v>sinian,gudu</v>
+      </c>
+      <c r="G476" t="str">
+        <v>想见见不到、话也说不出，发这句道尽此时心情。</v>
+      </c>
+      <c r="H476" t="str">
+        <v/>
+      </c>
+      <c r="I476" t="str">
+        <v>相思相见到哪天？此时此夜最是难熬。</v>
+      </c>
+    </row>
+    <row r="477">
+      <c r="A477" t="str">
+        <v>念去去，千里烟波，暮霭沉沉楚天阔。</v>
+      </c>
+      <c r="B477" t="str">
+        <v>柳永</v>
+      </c>
+      <c r="C477" t="str">
+        <v>雨霖铃</v>
+      </c>
+      <c r="D477" t="str">
+        <v>宋</v>
+      </c>
+      <c r="E477" t="str">
+        <v>wuji</v>
+      </c>
+      <c r="F477" t="str">
+        <v>sinian,gudu</v>
+      </c>
+      <c r="G477" t="str">
+        <v>送别后那句没说清的话，用这句托给远方的烟波。</v>
+      </c>
+      <c r="H477" t="str">
+        <v/>
+      </c>
+      <c r="I477" t="str">
+        <v>这一去千里烟波，楚天空阔暮霭沉沉——话留在了风里。</v>
+      </c>
+    </row>
+    <row r="478">
+      <c r="A478" t="str">
+        <v>相识满天下，知心能几人。</v>
+      </c>
+      <c r="B478" t="str">
+        <v>《增广贤文》</v>
+      </c>
+      <c r="C478" t="str">
+        <v>增广贤文</v>
+      </c>
+      <c r="D478" t="str">
+        <v>近代</v>
+      </c>
+      <c r="E478" t="str">
+        <v>shujiao</v>
+      </c>
+      <c r="F478" t="str">
+        <v>zhenxi,gudu</v>
+      </c>
+      <c r="G478" t="str">
+        <v>翻通讯录感慨，发这句讲知心难求。</v>
+      </c>
+      <c r="H478" t="str">
+        <v/>
+      </c>
+      <c r="I478" t="str">
+        <v>认识的人遍布天下，真正知心的能有几个。</v>
+      </c>
+    </row>
+    <row r="479">
+      <c r="A479" t="str">
+        <v>人生得一知己足矣，斯世当以同怀视之。</v>
+      </c>
+      <c r="B479" t="str">
+        <v>鲁迅</v>
+      </c>
+      <c r="C479" t="str">
+        <v>赠瞿秋白</v>
+      </c>
+      <c r="D479" t="str">
+        <v>现代</v>
+      </c>
+      <c r="E479" t="str">
+        <v>shujiao</v>
+      </c>
+      <c r="F479" t="str">
+        <v>zhenxi,zhenxi</v>
+      </c>
+      <c r="G479" t="str">
+        <v>那个很久不聊却一直在的朋友，发这句给他。</v>
+      </c>
+      <c r="H479" t="str">
+        <v/>
+      </c>
+      <c r="I479" t="str">
+        <v>人生有一个知己就够了，这辈子该当他同心人看待。</v>
+      </c>
+    </row>
+    <row r="480">
+      <c r="A480" t="str">
+        <v>故人入我梦，明我长相忆。</v>
+      </c>
+      <c r="B480" t="str">
+        <v>杜甫</v>
+      </c>
+      <c r="C480" t="str">
+        <v>梦李白</v>
+      </c>
+      <c r="D480" t="str">
+        <v>唐</v>
+      </c>
+      <c r="E480" t="str">
+        <v>shujiao</v>
+      </c>
+      <c r="F480" t="str">
+        <v>sinian,zhenxi</v>
+      </c>
+      <c r="G480" t="str">
+        <v>偶尔梦见老友，发这句说我还记着你。</v>
+      </c>
+      <c r="H480" t="str">
+        <v/>
+      </c>
+      <c r="I480" t="str">
+        <v>老朋友进了我的梦，是知道我一直惦念他。</v>
+      </c>
+    </row>
+    <row r="481">
+      <c r="A481" t="str">
+        <v>洛阳亲友如相问，一片冰心在玉壶。</v>
+      </c>
+      <c r="B481" t="str">
+        <v>王昌龄</v>
+      </c>
+      <c r="C481" t="str">
+        <v>芙蓉楼送辛渐</v>
+      </c>
+      <c r="D481" t="str">
+        <v>唐</v>
+      </c>
+      <c r="E481" t="str">
+        <v>shujiao</v>
+      </c>
+      <c r="F481" t="str">
+        <v>zhenxi,zhenxi</v>
+      </c>
+      <c r="G481" t="str">
+        <v>和老朋友断了联系但心没变，用这句表个态。</v>
+      </c>
+      <c r="H481" t="str">
+        <v/>
+      </c>
+      <c r="I481" t="str">
+        <v>洛阳亲友若问起我，就说我心像玉壶里的冰一样清。</v>
+      </c>
+    </row>
+    <row r="482">
+      <c r="A482" t="str">
+        <v>长亭外，古道边，芳草碧连天。</v>
+      </c>
+      <c r="B482" t="str">
+        <v>李叔同</v>
+      </c>
+      <c r="C482" t="str">
+        <v>送别</v>
+      </c>
+      <c r="D482" t="str">
+        <v>近代</v>
+      </c>
+      <c r="E482" t="str">
+        <v>biye</v>
+      </c>
+      <c r="F482" t="str">
+        <v>sinian</v>
+      </c>
+      <c r="G482" t="str">
+        <v>毕业季送同窗，用这句当背景音乐般的注脚。</v>
+      </c>
+      <c r="H482" t="str">
+        <v/>
+      </c>
+      <c r="I482" t="str">
+        <v>长亭外古道边，连天芳草碧绿——离别的景色。</v>
+      </c>
+    </row>
+    <row r="483">
+      <c r="A483" t="str">
+        <v>犬吠水声中，桃花带露浓。</v>
+      </c>
+      <c r="B483" t="str">
+        <v>李白</v>
+      </c>
+      <c r="C483" t="str">
+        <v>访戴天山道士不遇</v>
+      </c>
+      <c r="D483" t="str">
+        <v>唐</v>
+      </c>
+      <c r="E483" t="str">
+        <v>maogou</v>
+      </c>
+      <c r="F483" t="str">
+        <v>xinshang,wennuan</v>
+      </c>
+      <c r="G483" t="str">
+        <v>带狗溜进山里，拍张照配这句。</v>
+      </c>
+      <c r="H483" t="str">
+        <v/>
+      </c>
+      <c r="I483" t="str">
+        <v>狗叫声混在流水里，带露的桃花格外浓艳。</v>
+      </c>
+    </row>
+    <row r="484">
+      <c r="A484" t="str">
+        <v>晚日寒鸦一片愁，柳塘新绿却温柔。</v>
+      </c>
+      <c r="B484" t="str">
+        <v>辛弃疾</v>
+      </c>
+      <c r="C484" t="str">
+        <v>鹧鸪天</v>
+      </c>
+      <c r="D484" t="str">
+        <v>宋</v>
+      </c>
+      <c r="E484" t="str">
+        <v>maogou</v>
+      </c>
+      <c r="F484" t="str">
+        <v>wennuan,xinshang</v>
+      </c>
+      <c r="G484" t="str">
+        <v>遛狗时夕阳和寒鸦有点愁，池塘新绿又温柔，发这句写景。</v>
+      </c>
+      <c r="H484" t="str">
+        <v/>
+      </c>
+      <c r="I484" t="str">
+        <v>夕阳寒鸦一片愁，柳塘新绿却温柔——陪动物的傍晚。</v>
+      </c>
+    </row>
+    <row r="485">
+      <c r="A485" t="str">
+        <v>亦余心之所善兮，虽九死其犹未悔。</v>
+      </c>
+      <c r="B485" t="str">
+        <v>屈原</v>
+      </c>
+      <c r="C485" t="str">
+        <v>离骚</v>
+      </c>
+      <c r="D485" t="str">
+        <v>战国</v>
+      </c>
+      <c r="E485" t="str">
+        <v>suibo</v>
+      </c>
+      <c r="F485" t="str">
+        <v>jueqiang,buping</v>
+      </c>
+      <c r="G485" t="str">
+        <v>别人都卷你偏不，发这句亮明自己的坚持。</v>
+      </c>
+      <c r="H485" t="str">
+        <v/>
+      </c>
+      <c r="I485" t="str">
+        <v>只要是我心里认准的好，死九回也不后悔。</v>
+      </c>
+    </row>
+    <row r="486">
+      <c r="A486" t="str">
+        <v>安能摧眉折腰事权贵，使我不得开心颜。</v>
+      </c>
+      <c r="B486" t="str">
+        <v>李白</v>
+      </c>
+      <c r="C486" t="str">
+        <v>梦游天姥吟留别</v>
+      </c>
+      <c r="D486" t="str">
+        <v>唐</v>
+      </c>
+      <c r="E486" t="str">
+        <v>suibo</v>
+      </c>
+      <c r="F486" t="str">
+        <v>jueqiang,kuangxi</v>
+      </c>
+      <c r="G486" t="str">
+        <v>不想点头哈腰跟风，用这句说清楚底线。</v>
+      </c>
+      <c r="H486" t="str">
+        <v/>
+      </c>
+      <c r="I486" t="str">
+        <v>怎能让低眉弯腰去讨好权贵，弄丢自己的笑脸。</v>
+      </c>
+    </row>
+    <row r="487">
+      <c r="A487" t="str">
+        <v>和而不同。</v>
+      </c>
+      <c r="B487" t="str">
+        <v>孔子</v>
+      </c>
+      <c r="C487" t="str">
+        <v>论语·子路</v>
+      </c>
+      <c r="D487" t="str">
+        <v>先秦</v>
+      </c>
+      <c r="E487" t="str">
+        <v>suibo</v>
+      </c>
+      <c r="F487" t="str">
+        <v>chaoran,pingjing</v>
+      </c>
+      <c r="G487" t="str">
+        <v>不跟风但也不杠，发这句表明你的温和态度。</v>
+      </c>
+      <c r="H487" t="str">
+        <v/>
+      </c>
+      <c r="I487" t="str">
+        <v>和睦相处却不盲目附和——各有各的标准。</v>
+      </c>
+    </row>
+    <row r="488">
+      <c r="A488" t="str">
+        <v>众人皆有余，而我独若遗。</v>
+      </c>
+      <c r="B488" t="str">
+        <v>老子</v>
+      </c>
+      <c r="C488" t="str">
+        <v>道德经</v>
+      </c>
+      <c r="D488" t="str">
+        <v>先秦</v>
+      </c>
+      <c r="E488" t="str">
+        <v>suibo</v>
+      </c>
+      <c r="F488" t="str">
+        <v>chaoran,canglang</v>
+      </c>
+      <c r="G488" t="str">
+        <v>周围人都很满，你偏想留白，发这句说清楚。</v>
+      </c>
+      <c r="H488" t="str">
+        <v/>
+      </c>
+      <c r="I488" t="str">
+        <v>大家都很丰足，唯独我像有所遗漏——我自在我。</v>
+      </c>
+    </row>
+    <row r="489">
+      <c r="A489" t="str">
+        <v>不畏浮云遮望眼，自缘身在最高层。</v>
+      </c>
+      <c r="B489" t="str">
+        <v>王安石</v>
+      </c>
+      <c r="C489" t="str">
+        <v>登飞来峰</v>
+      </c>
+      <c r="D489" t="str">
+        <v>宋</v>
+      </c>
+      <c r="E489" t="str">
+        <v>gaochu</v>
+      </c>
+      <c r="F489" t="str">
+        <v>zhuangzhi,chaoran</v>
+      </c>
+      <c r="G489" t="str">
+        <v>站得高看得远，用这句讲格局。</v>
+      </c>
+      <c r="H489" t="str">
+        <v/>
+      </c>
+      <c r="I489" t="str">
+        <v>不怕浮云挡视线，只因我站在最高处。</v>
+      </c>
+    </row>
+    <row r="490">
+      <c r="A490" t="str">
+        <v>老骥伏枥，志在千里；烈士暮年，壮心不已。</v>
+      </c>
+      <c r="B490" t="str">
+        <v>曹操</v>
+      </c>
+      <c r="C490" t="str">
+        <v>龟虽寿</v>
+      </c>
+      <c r="D490" t="str">
+        <v>汉</v>
+      </c>
+      <c r="E490" t="str">
+        <v>shiye</v>
+      </c>
+      <c r="F490" t="str">
+        <v>zhuangzhi,haomai</v>
+      </c>
+      <c r="G490" t="str">
+        <v>年纪不小又被优化，发这句说雄心还在。</v>
+      </c>
+      <c r="H490" t="str">
+        <v/>
+      </c>
+      <c r="I490" t="str">
+        <v>老马伏在槽边仍想驰千里，有志之士年老雄心不减。</v>
+      </c>
+    </row>
+    <row r="491">
+      <c r="A491" t="str">
+        <v>莫嫌旧日云中守，犹堪一战取功勋。</v>
+      </c>
+      <c r="B491" t="str">
+        <v>王维</v>
+      </c>
+      <c r="C491" t="str">
+        <v>老将行</v>
+      </c>
+      <c r="D491" t="str">
+        <v>唐</v>
+      </c>
+      <c r="E491" t="str">
+        <v>shiye</v>
+      </c>
+      <c r="F491" t="str">
+        <v>zhuangzhi,jueqiang</v>
+      </c>
+      <c r="G491" t="str">
+        <v>被嫌弃老了过时，用这句说还能再拼一场。</v>
+      </c>
+      <c r="H491" t="str">
+        <v/>
+      </c>
+      <c r="I491" t="str">
+        <v>别嫌老将，还能再立战功。</v>
+      </c>
+    </row>
+    <row r="492">
+      <c r="A492" t="str">
+        <v>江流天地外，山色有无中。</v>
+      </c>
+      <c r="B492" t="str">
+        <v>王维</v>
+      </c>
+      <c r="C492" t="str">
+        <v>汉江临泛</v>
+      </c>
+      <c r="D492" t="str">
+        <v>唐</v>
+      </c>
+      <c r="E492" t="str">
+        <v>gaochu</v>
+      </c>
+      <c r="F492" t="str">
+        <v>xinshang,chaoran</v>
+      </c>
+      <c r="G492" t="str">
+        <v>飞机上或高楼望江，用这句写那点朦胧的远。</v>
+      </c>
+      <c r="H492" t="str">
+        <v/>
+      </c>
+      <c r="I492" t="str">
+        <v>江水好像流到天地外，山色在有无之间。</v>
+      </c>
+    </row>
+    <row r="493">
+      <c r="A493" t="str">
+        <v>荡胸生曾云，决眦入归鸟。</v>
+      </c>
+      <c r="B493" t="str">
+        <v>杜甫</v>
+      </c>
+      <c r="C493" t="str">
+        <v>望岳</v>
+      </c>
+      <c r="D493" t="str">
+        <v>唐</v>
+      </c>
+      <c r="E493" t="str">
+        <v>gaochu</v>
+      </c>
+      <c r="F493" t="str">
+        <v>xinshang,haomai</v>
+      </c>
+      <c r="G493" t="str">
+        <v>登顶远眺胸口一敞，发这句描那口被打开的气。</v>
+      </c>
+      <c r="H493" t="str">
+        <v/>
+      </c>
+      <c r="I493" t="str">
+        <v>层云升腾涤荡胸怀，睁裂眼睛送归鸟入山。</v>
+      </c>
+    </row>
+    <row r="494">
+      <c r="A494" t="str">
+        <v>九万里风鹏正举。</v>
+      </c>
+      <c r="B494" t="str">
+        <v>李清照</v>
+      </c>
+      <c r="C494" t="str">
+        <v>渔家傲</v>
+      </c>
+      <c r="D494" t="str">
+        <v>宋</v>
+      </c>
+      <c r="E494" t="str">
+        <v>shengzhi</v>
+      </c>
+      <c r="F494" t="str">
+        <v>haomai,zhuangzhi</v>
+      </c>
+      <c r="G494" t="str">
+        <v>被看见、被重用时，用这句配你正起的风。</v>
+      </c>
+      <c r="H494" t="str">
+        <v/>
+      </c>
+      <c r="I494" t="str">
+        <v>乘着九万里长风，大鹏正展翅高飞。</v>
+      </c>
+    </row>
+    <row r="495">
+      <c r="A495" t="str">
+        <v>好风凭借力，送我上青云。</v>
+      </c>
+      <c r="B495" t="str">
+        <v>曹雪芹</v>
+      </c>
+      <c r="C495" t="str">
+        <v>红楼梦·临江仙</v>
+      </c>
+      <c r="D495" t="str">
+        <v>清</v>
+      </c>
+      <c r="E495" t="str">
+        <v>shengzhi</v>
+      </c>
+      <c r="F495" t="str">
+        <v>zhuangzhi,kuangxi</v>
+      </c>
+      <c r="G495" t="str">
+        <v>借势上位、抓住机会，发这句不谦虚地得意一下。</v>
+      </c>
+      <c r="H495" t="str">
+        <v/>
+      </c>
+      <c r="I495" t="str">
+        <v>借好风的力量，送我直上青云。</v>
+      </c>
+    </row>
+    <row r="496">
+      <c r="A496" t="str">
+        <v>大丈夫处世，当扫除天下。</v>
+      </c>
+      <c r="B496" t="str">
+        <v>《后汉书》</v>
+      </c>
+      <c r="C496" t="str">
+        <v>陈蕃传</v>
+      </c>
+      <c r="D496" t="str">
+        <v>汉</v>
+      </c>
+      <c r="E496" t="str">
+        <v>shengzhi</v>
+      </c>
+      <c r="F496" t="str">
+        <v>zhuangzhi,haomai</v>
+      </c>
+      <c r="G496" t="str">
+        <v>刚挑大梁，用这句表你打算干票大的。</v>
+      </c>
+      <c r="H496" t="str">
+        <v/>
+      </c>
+      <c r="I496" t="str">
+        <v>大丈夫活在世上，就该扫清天下不平事。</v>
+      </c>
+    </row>
+    <row r="497">
+      <c r="A497" t="str">
+        <v>业精于勤，荒于嬉。</v>
+      </c>
+      <c r="B497" t="str">
+        <v>韩愈</v>
+      </c>
+      <c r="C497" t="str">
+        <v>进学解</v>
+      </c>
+      <c r="D497" t="str">
+        <v>唐</v>
+      </c>
+      <c r="E497" t="str">
+        <v>jiaban</v>
+      </c>
+      <c r="F497" t="str">
+        <v>zhenxi,chaoran</v>
+      </c>
+      <c r="G497" t="str">
+        <v>用这句给连轴转的自己一个正名。</v>
+      </c>
+      <c r="H497" t="str">
+        <v/>
+      </c>
+      <c r="I497" t="str">
+        <v>学业的精进靠勤奋，荒废在嬉闹里。</v>
+      </c>
+    </row>
+    <row r="498">
+      <c r="A498" t="str">
+        <v>积土而为山，积水而为海。</v>
+      </c>
+      <c r="B498" t="str">
+        <v>荀子</v>
+      </c>
+      <c r="C498" t="str">
+        <v>劝学</v>
+      </c>
+      <c r="D498" t="str">
+        <v>先秦</v>
+      </c>
+      <c r="E498" t="str">
+        <v>jiaban</v>
+      </c>
+      <c r="F498" t="str">
+        <v>zhenxi,zhuangzhi</v>
+      </c>
+      <c r="G498" t="str">
+        <v>日拱一卒的加班，发这句说量变会成。</v>
+      </c>
+      <c r="H498" t="str">
+        <v/>
+      </c>
+      <c r="I498" t="str">
+        <v>积土成山，积水成海——一点点攒出来的。</v>
+      </c>
+    </row>
+    <row r="499">
+      <c r="A499" t="str">
+        <v>恰同学少年，风华正茂；书生意气，挥斥方遒。</v>
+      </c>
+      <c r="B499" t="str">
+        <v>毛泽东</v>
+      </c>
+      <c r="C499" t="str">
+        <v>沁园春·长沙</v>
+      </c>
+      <c r="D499" t="str">
+        <v>现代</v>
+      </c>
+      <c r="E499" t="str">
+        <v>biye</v>
+      </c>
+      <c r="F499" t="str">
+        <v>haomai,kuangxi</v>
+      </c>
+      <c r="G499" t="str">
+        <v>毕业回望校园时光，发这句最青春。</v>
+      </c>
+      <c r="H499" t="str">
+        <v/>
+      </c>
+      <c r="I499" t="str">
+        <v>同学们正青春，风采才华横溢，意气风发。</v>
+      </c>
+    </row>
+    <row r="500">
+      <c r="A500" t="str">
+        <v>宣父犹能畏后生，丈夫未可轻年少。</v>
+      </c>
+      <c r="B500" t="str">
+        <v>李白</v>
+      </c>
+      <c r="C500" t="str">
+        <v>上李邕</v>
+      </c>
+      <c r="D500" t="str">
+        <v>唐</v>
+      </c>
+      <c r="E500" t="str">
+        <v>luobang</v>
+      </c>
+      <c r="F500" t="str">
+        <v>zhuangzhi,haomai</v>
+      </c>
+      <c r="G500" t="str">
+        <v>被说你太年轻不行，用这句回敬。</v>
+      </c>
+      <c r="H500" t="str">
+        <v/>
+      </c>
+      <c r="I500" t="str">
+        <v>孔子尚且敬畏后生，大丈夫别小看年轻人。</v>
+      </c>
+    </row>
+    <row r="501">
+      <c r="A501" t="str">
+        <v>咬定青山不放松，立根原在破岩中。</v>
+      </c>
+      <c r="B501" t="str">
+        <v>郑燮</v>
+      </c>
+      <c r="C501" t="str">
+        <v>竹石</v>
+      </c>
+      <c r="D501" t="str">
+        <v>清</v>
+      </c>
+      <c r="E501" t="str">
+        <v>shiye</v>
+      </c>
+      <c r="F501" t="str">
+        <v>jueqiang,zhenxi</v>
+      </c>
+      <c r="G501" t="str">
+        <v>丢了工作但根基还在，用这句说你站得稳。</v>
+      </c>
+      <c r="H501" t="str">
+        <v/>
+      </c>
+      <c r="I501" t="str">
+        <v>竹根咬定青山不松，生在破岩里也立得住。</v>
+      </c>
+    </row>
+    <row r="502">
+      <c r="A502" t="str">
+        <v>精卫衔微木，将以填沧海。</v>
+      </c>
+      <c r="B502" t="str">
+        <v>陶渊明</v>
+      </c>
+      <c r="C502" t="str">
+        <v>读山海经</v>
+      </c>
+      <c r="D502" t="str">
+        <v>晋</v>
+      </c>
+      <c r="E502" t="str">
+        <v>shiye</v>
+      </c>
+      <c r="F502" t="str">
+        <v>jueqiang,zhuangzhi</v>
+      </c>
+      <c r="G502" t="str">
+        <v>起点低也要干，用这句说小力量也能成事。</v>
+      </c>
+      <c r="H502" t="str">
+        <v/>
+      </c>
+      <c r="I502" t="str">
+        <v>精卫叼小木，想填平沧海——认准了就做。</v>
+      </c>
+    </row>
+    <row r="503">
+      <c r="A503" t="str">
+        <v>黄河落天走东海，万里写入胸怀间。</v>
+      </c>
+      <c r="B503" t="str">
+        <v>李白</v>
+      </c>
+      <c r="C503" t="str">
+        <v>赠裴十四</v>
+      </c>
+      <c r="D503" t="str">
+        <v>唐</v>
+      </c>
+      <c r="E503" t="str">
+        <v>gaochu</v>
+      </c>
+      <c r="F503" t="str">
+        <v>haomai,xinshang</v>
+      </c>
+      <c r="G503" t="str">
+        <v>高处看大河奔流，发这句把气势收进胸怀。</v>
+      </c>
+      <c r="H503" t="str">
+        <v/>
+      </c>
+      <c r="I503" t="str">
+        <v>黄河从天而落奔向东海，万里风光写进胸襟。</v>
+      </c>
+    </row>
+    <row r="504">
+      <c r="A504" t="str">
+        <v>物是人非事事休，欲语泪先流。</v>
+      </c>
+      <c r="B504" t="str">
+        <v>李清照</v>
+      </c>
+      <c r="C504" t="str">
+        <v>武陵春</v>
+      </c>
+      <c r="D504" t="str">
+        <v>宋</v>
+      </c>
+      <c r="E504" t="str">
+        <v>jiuzhao</v>
+      </c>
+      <c r="F504" t="str">
+        <v>sinian,gudu</v>
+      </c>
+      <c r="G504" t="str">
+        <v>旧物还在人已不在，发这句最沉。</v>
+      </c>
+      <c r="H504" t="str">
+        <v/>
+      </c>
+      <c r="I504" t="str">
+        <v>景物依旧人事全非，话没出口泪先流。</v>
+      </c>
+    </row>
+    <row r="505">
+      <c r="A505" t="str">
+        <v>成功不是终点，失败也非末日，唯有继续前行的勇气才重要。</v>
+      </c>
+      <c r="B505" t="str">
+        <v>丘吉尔</v>
+      </c>
+      <c r="C505" t="str">
+        <v>演讲</v>
+      </c>
+      <c r="D505" t="str">
+        <v>英国</v>
+      </c>
+      <c r="E505" t="str">
+        <v>shiye</v>
+      </c>
+      <c r="F505" t="str">
+        <v>zhuangzhi,jueqiang</v>
+      </c>
+      <c r="G505" t="str">
+        <v>被裁或创业失败，发这句稳住继续干的勇气。</v>
+      </c>
+      <c r="H505" t="str">
+        <v>Success is not final, failure is not fatal: it is the courage to continue that counts.</v>
+      </c>
+      <c r="I505" t="str">
+        <v>输赢都不是句号，能接着走下去才是真本事。</v>
+      </c>
+    </row>
+    <row r="506">
+      <c r="A506" t="str">
+        <v>最好的出路，永远是穿过去。</v>
+      </c>
+      <c r="B506" t="str">
+        <v>罗伯特·弗罗斯特</v>
+      </c>
+      <c r="C506" t="str">
+        <v>诗</v>
+      </c>
+      <c r="D506" t="str">
+        <v>美国</v>
+      </c>
+      <c r="E506" t="str">
+        <v>shiye</v>
+      </c>
+      <c r="F506" t="str">
+        <v>jueqiang,chaoran</v>
+      </c>
+      <c r="G506" t="str">
+        <v>卡在低谷想绕路，用这句提醒自己直面它。</v>
+      </c>
+      <c r="H506" t="str">
+        <v>The best way out is always through.</v>
+      </c>
+      <c r="I506" t="str">
+        <v>别绕，穿过眼前的难处才是出口。</v>
+      </c>
+    </row>
+    <row r="507">
+      <c r="A507" t="str">
+        <v>摔倒七次，第八次站起来。</v>
+      </c>
+      <c r="B507" t="str">
+        <v>日本谚语</v>
+      </c>
+      <c r="C507" t="str">
+        <v>谚语</v>
+      </c>
+      <c r="D507" t="str">
+        <v>日本</v>
+      </c>
+      <c r="E507" t="str">
+        <v>shiye</v>
+      </c>
+      <c r="F507" t="str">
+        <v>jueqiang,zhuangzhi</v>
+      </c>
+      <c r="G507" t="str">
+        <v>连续被拒，发这句说你还会再起。</v>
+      </c>
+      <c r="H507" t="str">
+        <v>Fall seven times, stand up eight.</v>
+      </c>
+      <c r="I507" t="str">
+        <v>跌倒多少次都算数，关键是再站起来。</v>
+      </c>
+    </row>
+    <row r="508">
+      <c r="A508" t="str">
+        <v>平静的海面，练不出熟练的水手。</v>
+      </c>
+      <c r="B508" t="str">
+        <v>非洲谚语</v>
+      </c>
+      <c r="C508" t="str">
+        <v>谚语</v>
+      </c>
+      <c r="D508" t="str">
+        <v>非洲</v>
+      </c>
+      <c r="E508" t="str">
+        <v>shiye</v>
+      </c>
+      <c r="F508" t="str">
+        <v>jueqiang,zhenxi</v>
+      </c>
+      <c r="G508" t="str">
+        <v>把这段低谷当练级，发这句给自己正名。</v>
+      </c>
+      <c r="H508" t="str">
+        <v>Smooth seas do not make skillful sailors.</v>
+      </c>
+      <c r="I508" t="str">
+        <v>没风浪，就长不出真本事。</v>
+      </c>
+    </row>
+    <row r="509">
+      <c r="A509" t="str">
+        <v>山不厌高，海不厌深。</v>
+      </c>
+      <c r="B509" t="str">
+        <v>曹操</v>
+      </c>
+      <c r="C509" t="str">
+        <v>短歌行</v>
+      </c>
+      <c r="D509" t="str">
+        <v>汉</v>
+      </c>
+      <c r="E509" t="str">
+        <v>shiye</v>
+      </c>
+      <c r="F509" t="str">
+        <v>zhuangzhi,haomai</v>
+      </c>
+      <c r="G509" t="str">
+        <v>被需要、想被重用，发这句讲你还能接更多。</v>
+      </c>
+      <c r="H509" t="str">
+        <v/>
+      </c>
+      <c r="I509" t="str">
+        <v>山不嫌高，海不嫌深——我还能承载更多。</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:I461"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:I509"/>
   </ignoredErrors>
 </worksheet>
 </file>
